--- a/Results/ESM_15_Dimensions_xpad_2022_double_and_single_conical.xlsx
+++ b/Results/ESM_15_Dimensions_xpad_2022_double_and_single_conical.xlsx
@@ -1,46 +1,136 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\University of Dayton\Reseach in UD\new_graphs_july\Final results\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2CB467-14D8-4BFD-B227-93C2E2654572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Depth" sheetId="3" r:id="rId1"/>
-    <sheet name="Overlap_depth" sheetId="5" r:id="rId2"/>
-    <sheet name="Width" sheetId="4" r:id="rId3"/>
-    <sheet name="Overlap_width" sheetId="6" r:id="rId4"/>
-    <sheet name="errors" sheetId="1" r:id="rId5"/>
+    <sheet sheetId="1" name="Info" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Depth" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Overlap_depth" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Width" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Overlap_width" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="errors" state="visible" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Information</t>
+  </si>
+  <si>
+    <t>Online Resource</t>
+  </si>
+  <si>
+    <t>ESM_15</t>
+  </si>
+  <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
+    <t>NIST AM-Bench 2022</t>
+  </si>
+  <si>
+    <t>Simulation case</t>
+  </si>
+  <si>
+    <t>XPad multi-track</t>
+  </si>
+  <si>
+    <t>Heat-source models</t>
+  </si>
+  <si>
+    <t>Single-conical and Double Conical Heat Source (DCHS)</t>
+  </si>
+  <si>
+    <t>Number of simulated tracks</t>
+  </si>
+  <si>
+    <t>Track length</t>
+  </si>
+  <si>
+    <t>2 mm</t>
+  </si>
+  <si>
+    <t>Hatch spacing</t>
+  </si>
+  <si>
+    <t>110 µm</t>
+  </si>
+  <si>
+    <t>Laser power</t>
+  </si>
+  <si>
+    <t>285 W</t>
+  </si>
+  <si>
+    <t>Scan speed</t>
+  </si>
+  <si>
+    <t>960 mm/s</t>
+  </si>
+  <si>
+    <t>Laser spot diameter</t>
+  </si>
+  <si>
+    <t>67 µm</t>
+  </si>
+  <si>
+    <t>Turnaround time</t>
+  </si>
+  <si>
+    <t>5 ms after odd-numbered tracks and 40 ms after even-numbered tracks</t>
+  </si>
+  <si>
+    <t>Data included</t>
+  </si>
+  <si>
+    <t>Pad depth, overlap depth, pad width, overlap width, and comparison/error data</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>AM-Bench 2022 XPad multi-track validation and comparison of single-conical and DCHS models</t>
+  </si>
+  <si>
+    <t>Related simulation videos</t>
+  </si>
+  <si>
+    <t>ESM_3 and ESM_4</t>
+  </si>
+  <si>
+    <t>Related temperature-history videos</t>
+  </si>
+  <si>
+    <t>ESM_10 and ESM_11</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>All dimensional quantities are reported in µm unless otherwise specified. The data support the AM-Bench 2022 XPad multi-track validation presented in the main manuscript.</t>
+  </si>
+  <si>
+    <t>Track id</t>
+  </si>
+  <si>
+    <t>Single conical</t>
+  </si>
+  <si>
+    <t>Double Conical</t>
+  </si>
+  <si>
+    <t>Experiment standard deviation (%)</t>
+  </si>
+  <si>
+    <t>Double conical</t>
+  </si>
   <si>
     <t>Experiment</t>
   </si>
@@ -67,42 +157,56 @@
   </si>
   <si>
     <t>Solid Cooling Rate (°C/s)</t>
-  </si>
-  <si>
-    <t>Double conical</t>
-  </si>
-  <si>
-    <t>Single conical</t>
-  </si>
-  <si>
-    <t>Experiment standard deviation (%)</t>
-  </si>
-  <si>
-    <t>Track id</t>
-  </si>
-  <si>
-    <t>Double Conical</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
+    <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -117,16 +221,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -155,44 +273,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -222,12 +340,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -266,274 +384,463 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{286C93A2-AF33-4DD8-AB8E-AE5367FC8E0B}">
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="1" max="1" width="34.857142857142854" customWidth="1"/>
+    <col min="2" max="2" width="43.57142857142857" customWidth="1"/>
+    <col min="3" max="26" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <v>2</v>
-      </c>
-      <c r="D1">
-        <v>3</v>
-      </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-      <c r="F1">
-        <v>5</v>
-      </c>
-      <c r="G1">
-        <v>6</v>
-      </c>
-      <c r="H1">
-        <v>7</v>
-      </c>
-      <c r="I1">
-        <v>8</v>
-      </c>
-      <c r="J1">
-        <v>9</v>
-      </c>
-      <c r="K1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2">
-        <v>141.27000000000001</v>
-      </c>
-      <c r="C2">
-        <v>142.78</v>
-      </c>
-      <c r="D2">
-        <v>155.54</v>
-      </c>
-      <c r="E2">
-        <v>152.62</v>
-      </c>
-      <c r="F2">
-        <v>156.46</v>
-      </c>
-      <c r="G2">
-        <v>153.12</v>
-      </c>
-      <c r="H2">
-        <v>156.81</v>
-      </c>
-      <c r="I2">
-        <v>153.47999999999999</v>
-      </c>
-      <c r="J2">
-        <v>165.9</v>
-      </c>
-      <c r="K2">
-        <v>162.54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3">
-        <v>141.30000000000001</v>
-      </c>
-      <c r="C3">
-        <v>142.1</v>
-      </c>
-      <c r="D3">
-        <v>154.19999999999999</v>
-      </c>
-      <c r="E3">
-        <v>151.5</v>
-      </c>
-      <c r="F3">
-        <v>154.80000000000001</v>
-      </c>
-      <c r="G3">
-        <v>151.69999999999999</v>
-      </c>
-      <c r="H3">
-        <v>154.9</v>
-      </c>
-      <c r="I3">
-        <v>151.80000000000001</v>
-      </c>
-      <c r="J3">
-        <v>164</v>
-      </c>
-      <c r="K3">
-        <v>160.80000000000001</v>
-      </c>
+      <c r="B9" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="5"/>
+      <c r="B36" s="5"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84407C4A-1309-4A2A-8E36-B04B008A66ED}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.714285714285714" customWidth="1"/>
+    <col min="2" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -562,87 +869,98 @@
       <c r="J1">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="B2">
-        <v>80.150000000000006</v>
+        <v>141.27</v>
       </c>
       <c r="C2">
-        <v>97.79</v>
+        <v>142.78</v>
       </c>
       <c r="D2">
-        <v>98.45</v>
+        <v>155.54</v>
       </c>
       <c r="E2">
-        <v>103.84</v>
+        <v>152.62</v>
       </c>
       <c r="F2">
-        <v>101.71</v>
+        <v>156.46</v>
       </c>
       <c r="G2">
-        <v>105.71</v>
+        <v>153.12</v>
       </c>
       <c r="H2">
-        <v>103.17</v>
+        <v>156.81</v>
       </c>
       <c r="I2">
-        <v>109.1</v>
+        <v>153.48</v>
       </c>
       <c r="J2">
-        <v>107.58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>165.9</v>
+      </c>
+      <c r="K2">
+        <v>162.54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B3">
-        <v>59.7</v>
+        <v>141.3</v>
       </c>
       <c r="C3">
-        <v>75.900000000000006</v>
+        <v>142.1</v>
       </c>
       <c r="D3">
-        <v>75.2</v>
+        <v>154.2</v>
       </c>
       <c r="E3">
-        <v>80.8</v>
+        <v>151.5</v>
       </c>
       <c r="F3">
-        <v>77.900000000000006</v>
+        <v>154.8</v>
       </c>
       <c r="G3">
-        <v>82</v>
+        <v>151.7</v>
       </c>
       <c r="H3">
-        <v>79.099999999999994</v>
+        <v>154.9</v>
       </c>
       <c r="I3">
-        <v>83.8</v>
+        <v>151.8</v>
       </c>
       <c r="J3">
-        <v>81.3</v>
+        <v>164</v>
+      </c>
+      <c r="K3">
+        <v>160.8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B577218E-3815-488D-8AB8-FF4CFAC7D9EB}">
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" customWidth="1"/>
+    <col min="1" max="1" width="30.714285714285715" customWidth="1"/>
+    <col min="2" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -671,96 +989,89 @@
       <c r="J1">
         <v>9</v>
       </c>
-      <c r="K1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="B2">
-        <v>68.91</v>
+        <v>80.15</v>
       </c>
       <c r="C2">
-        <v>72.260000000000005</v>
+        <v>97.79</v>
       </c>
       <c r="D2">
-        <v>85.63</v>
+        <v>98.45</v>
       </c>
       <c r="E2">
-        <v>74.430000000000007</v>
+        <v>103.84</v>
       </c>
       <c r="F2">
-        <v>88.34</v>
+        <v>101.71</v>
       </c>
       <c r="G2">
-        <v>75.08</v>
+        <v>105.71</v>
       </c>
       <c r="H2">
-        <v>89.19</v>
+        <v>103.17</v>
       </c>
       <c r="I2">
-        <v>75.680000000000007</v>
+        <v>109.1</v>
       </c>
       <c r="J2">
-        <v>89.87</v>
-      </c>
-      <c r="K2">
-        <v>76.400000000000006</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+        <v>107.58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B3">
-        <v>67.7</v>
+        <v>59.7</v>
       </c>
       <c r="C3">
-        <v>70.599999999999994</v>
+        <v>75.9</v>
       </c>
       <c r="D3">
+        <v>75.2</v>
+      </c>
+      <c r="E3">
+        <v>80.8</v>
+      </c>
+      <c r="F3">
+        <v>77.9</v>
+      </c>
+      <c r="G3">
+        <v>82</v>
+      </c>
+      <c r="H3">
+        <v>79.1</v>
+      </c>
+      <c r="I3">
+        <v>83.8</v>
+      </c>
+      <c r="J3">
         <v>81.3</v>
-      </c>
-      <c r="E3">
-        <v>73.459999999999994</v>
-      </c>
-      <c r="F3">
-        <v>83.8</v>
-      </c>
-      <c r="G3">
-        <v>74.3</v>
-      </c>
-      <c r="H3">
-        <v>84.7</v>
-      </c>
-      <c r="I3">
-        <v>75</v>
-      </c>
-      <c r="J3">
-        <v>85.5</v>
-      </c>
-      <c r="K3">
-        <v>75.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72D2DF72-28FA-449D-B412-2EF332E77E60}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="1" max="1" width="18.428571428571427" customWidth="1"/>
+    <col min="2" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B1">
         <v>1</v>
@@ -789,268 +1100,381 @@
       <c r="J1">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="B2">
-        <v>106.58</v>
+        <v>68.91</v>
       </c>
       <c r="C2">
-        <v>96.65</v>
+        <v>72.26</v>
       </c>
       <c r="D2">
-        <v>121.15</v>
+        <v>85.63</v>
       </c>
       <c r="E2">
-        <v>96.14</v>
+        <v>74.43</v>
       </c>
       <c r="F2">
-        <v>123.16</v>
+        <v>88.34</v>
       </c>
       <c r="G2">
-        <v>96.01</v>
+        <v>75.08</v>
       </c>
       <c r="H2">
-        <v>123.47</v>
+        <v>89.19</v>
       </c>
       <c r="I2">
-        <v>95.74</v>
+        <v>75.68</v>
       </c>
       <c r="J2">
-        <v>123.56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>89.87</v>
+      </c>
+      <c r="K2">
+        <v>76.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B3">
-        <v>107.1</v>
+        <v>67.7</v>
       </c>
       <c r="C3">
-        <v>99.26</v>
+        <v>70.6</v>
       </c>
       <c r="D3">
-        <v>118.17</v>
+        <v>81.3</v>
       </c>
       <c r="E3">
-        <v>99.38</v>
+        <v>73.46</v>
       </c>
       <c r="F3">
-        <v>119.5</v>
+        <v>83.8</v>
       </c>
       <c r="G3">
-        <v>99.6</v>
+        <v>74.3</v>
       </c>
       <c r="H3">
-        <v>119.77</v>
+        <v>84.7</v>
       </c>
       <c r="I3">
-        <v>99.47</v>
+        <v>75</v>
       </c>
       <c r="J3">
-        <v>119.98</v>
+        <v>85.5</v>
+      </c>
+      <c r="K3">
+        <v>75.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="20.285714285714285" customWidth="1"/>
+    <col min="2" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2">
+        <v>106.58</v>
+      </c>
+      <c r="C2">
+        <v>96.65</v>
+      </c>
+      <c r="D2">
+        <v>121.15</v>
+      </c>
+      <c r="E2">
+        <v>96.14</v>
+      </c>
+      <c r="F2">
+        <v>123.16</v>
+      </c>
+      <c r="G2">
+        <v>96.01</v>
+      </c>
+      <c r="H2">
+        <v>123.47</v>
+      </c>
+      <c r="I2">
+        <v>95.74</v>
+      </c>
+      <c r="J2">
+        <v>123.56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3">
+        <v>107.1</v>
+      </c>
+      <c r="C3">
+        <v>99.26</v>
+      </c>
+      <c r="D3">
+        <v>118.17</v>
+      </c>
+      <c r="E3">
+        <v>99.38</v>
+      </c>
+      <c r="F3">
+        <v>119.5</v>
+      </c>
+      <c r="G3">
+        <v>99.6</v>
+      </c>
+      <c r="H3">
+        <v>119.77</v>
+      </c>
+      <c r="I3">
+        <v>99.47</v>
+      </c>
+      <c r="J3">
+        <v>119.98</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="24" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="7"/>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="C2" s="6"/>
       <c r="D2" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1">
+        <v>41</v>
+      </c>
+      <c r="B3" s="8">
         <v>159.6</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="8">
         <v>3.3834586466165417</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="8">
         <v>164.61</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="8">
         <f>ABS((D3-B3)/B3*100)</f>
-        <v>3.1390977443609143</v>
-      </c>
-      <c r="F3" s="1">
+      </c>
+      <c r="F3" s="8">
         <v>167.1</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="8">
         <f>ABS((F3-B3)/B3*100)</f>
-        <v>4.6992481203007523</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1">
+        <v>42</v>
+      </c>
+      <c r="B4" s="8">
         <v>83.9</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="8">
         <v>15.137067938021453</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="8">
         <v>81.47</v>
       </c>
-      <c r="E4" s="1">
-        <f t="shared" ref="E4:E8" si="0">ABS((D4-B4)/B4*100)</f>
-        <v>2.8963051251489946</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" s="8">
+        <f>ABS((D4-B4)/B4*100)</f>
+      </c>
+      <c r="F4" s="8">
         <v>107.39</v>
       </c>
-      <c r="G4" s="1">
-        <f t="shared" ref="G4:G8" si="1">ABS((F4-B4)/B4*100)</f>
-        <v>27.997616209773529</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G4" s="8">
+        <f>ABS((F4-B4)/B4*100)</f>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1">
+        <v>43</v>
+      </c>
+      <c r="B5" s="8">
         <v>93.1</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="8">
         <v>4.9409237379162185</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="8">
         <v>80.38</v>
       </c>
-      <c r="E5" s="1">
-        <f t="shared" si="0"/>
-        <v>13.662728249194414</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" s="8">
+        <f>ABS((D5-B5)/B5*100)</f>
+      </c>
+      <c r="F5" s="8">
         <v>82.62</v>
       </c>
-      <c r="G5" s="1">
-        <f t="shared" si="1"/>
-        <v>11.256713211600418</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G5" s="8">
+        <f>ABS((F5-B5)/B5*100)</f>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1">
+        <v>44</v>
+      </c>
+      <c r="B6" s="8">
         <v>104.55</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="8">
         <v>14.82544237207078</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="8">
         <v>114.08</v>
       </c>
-      <c r="E6" s="1">
-        <f t="shared" si="0"/>
-        <v>9.1152558584409391</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" s="8">
+        <f>ABS((D6-B6)/B6*100)</f>
+      </c>
+      <c r="F6" s="8">
         <v>115.35</v>
       </c>
-      <c r="G6" s="1">
-        <f t="shared" si="1"/>
-        <v>10.329985652797703</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G6" s="8">
+        <f>ABS((F6-B6)/B6*100)</f>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="C7" s="1">
+        <v>45</v>
+      </c>
+      <c r="B7" s="8">
+        <v>0.0012</v>
+      </c>
+      <c r="C7" s="8">
         <v>18.666666666666668</v>
       </c>
-      <c r="D7" s="2">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="E7" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1.3699999999999999E-3</v>
-      </c>
-      <c r="G7" s="1">
-        <f t="shared" si="1"/>
-        <v>14.16666666666667</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D7" s="8">
+        <v>0.0012</v>
+      </c>
+      <c r="E7" s="8">
+        <f>ABS((D7-B7)/B7*100)</f>
+      </c>
+      <c r="F7" s="8">
+        <v>0.00137</v>
+      </c>
+      <c r="G7" s="8">
+        <f>ABS((F7-B7)/B7*100)</f>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2">
+        <v>46</v>
+      </c>
+      <c r="B8" s="8">
         <v>324000</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="8">
         <v>53.086419753086425</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="8">
         <v>483000</v>
       </c>
-      <c r="E8" s="1">
-        <f t="shared" si="0"/>
-        <v>49.074074074074076</v>
-      </c>
-      <c r="F8" s="2">
+      <c r="E8" s="8">
+        <f>ABS((D8-B8)/B8*100)</f>
+      </c>
+      <c r="F8" s="8">
         <v>420000</v>
       </c>
-      <c r="G8" s="1">
-        <f t="shared" si="1"/>
-        <v>29.629629629629626</v>
+      <c r="G8" s="8">
+        <f>ABS((F8-B8)/B8*100)</f>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D1:E1"/>
     <mergeCell ref="C1:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>